--- a/dcf/EPD.xlsx
+++ b/dcf/EPD.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04157597945452468</v>
+        <v>0.04162091392806828</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.04657597945452468</v>
+        <v>0.04662091392806828</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05157597945452468</v>
+        <v>0.05162091392806829</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.05657597945452468</v>
+        <v>0.05662091392806828</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06157597945452468</v>
+        <v>0.06162091392806828</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.06657597945452468</v>
+        <v>0.06662091392806828</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07157597945452468</v>
+        <v>0.07162091392806828</v>
       </c>
     </row>
     <row r="5">
@@ -1145,25 +1145,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>74.22028201174032</v>
+        <v>74.18883910142212</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>70.80519162069896</v>
+        <v>70.77525207253812</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>67.5528923365338</v>
+        <v>67.52437548938192</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>64.45467261000933</v>
+        <v>64.427502536229</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>61.50233086795379</v>
+        <v>61.47643607342601</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>58.6881432692641</v>
+        <v>58.66345641376186</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>56.00483364483713</v>
+        <v>55.98129128129267</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>80.22294229218052</v>
+        <v>80.18891039750893</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>76.52716318143625</v>
+        <v>76.49476749936775</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>73.00854547400554</v>
+        <v>72.97769794127134</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>69.65757875922949</v>
+        <v>69.62819649079702</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>66.46531049033555</v>
+        <v>66.43731545077409</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>63.4233106632224</v>
+        <v>63.39662936040201</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>60.52363889006295</v>
+        <v>60.49820208957097</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>86.22560257262067</v>
+        <v>86.18898169359574</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>82.24913474217355</v>
+        <v>82.21428292619738</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>78.4641986114773</v>
+        <v>78.43102039316076</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>74.86048490844968</v>
+        <v>74.82889044536506</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>71.42829011271731</v>
+        <v>71.39819482812219</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>68.1584780571807</v>
+        <v>68.12980230704217</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>65.04244413528878</v>
+        <v>65.01511289784926</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>92.22826285306087</v>
+        <v>92.18905298968255</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>87.97110630291083</v>
+        <v>87.93379835302704</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>83.91985174894907</v>
+        <v>83.88434284505017</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>80.06339105766986</v>
+        <v>80.02958439993309</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>76.39126973509906</v>
+        <v>76.35907420547029</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>72.89364545113899</v>
+        <v>72.86297525368235</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>69.5612493805146</v>
+        <v>69.53202370612759</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>98.23092313350105</v>
+        <v>98.18912428576937</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>93.69307786364813</v>
+        <v>93.65331377985666</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>89.37550488642084</v>
+        <v>89.33766529693959</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>85.26629720689004</v>
+        <v>85.23027835450114</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>81.35424935748082</v>
+        <v>81.31995358281837</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>77.6288128450973</v>
+        <v>77.59614820032252</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>74.08005462574043</v>
+        <v>74.0489345144059</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>104.2335834139412</v>
+        <v>104.1891955818562</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>99.41504942438542</v>
+        <v>99.37282920668629</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>94.83115802389258</v>
+        <v>94.790987748829</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>90.46920335611021</v>
+        <v>90.43097230906915</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>86.31722897986258</v>
+        <v>86.28083296016646</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>82.36398023905561</v>
+        <v>82.32932114696267</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>78.59885987096624</v>
+        <v>78.5658453226842</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>110.2362436943814</v>
+        <v>110.189266877943</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>105.1370209851227</v>
+        <v>105.0923446335159</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>100.2868111613643</v>
+        <v>100.2443102007184</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>95.6721095053304</v>
+        <v>95.6316662636372</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>91.28020860224434</v>
+        <v>91.24171233751456</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>87.09914763301391</v>
+        <v>87.06249409360284</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>83.11766511619207</v>
+        <v>83.08275613096249</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>36.75</v>
+        <v>37.01499938964844</v>
       </c>
     </row>
     <row r="14">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.05657597945452468</v>
+        <v>0.05662091392806828</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.06205282702093</v>
+        <v>1.0620714438066</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>36.75</v>
+        <v>37.01499938964844</v>
       </c>
     </row>
     <row r="49">
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>80.06339105766986</v>
+        <v>80.02958439993309</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>123.3920534610143</v>
+        <v>123.3412619737263</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>48.95432619895693</v>
+        <v>48.93250611557799</v>
       </c>
     </row>
     <row r="59">
